--- a/Final Project/Final Submission/Spring 2026 HTML Code for PowerBI.xlsx
+++ b/Final Project/Final Submission/Spring 2026 HTML Code for PowerBI.xlsx
@@ -197,7 +197,7 @@
 &lt;div id="plotly-div"&gt;&lt;/div&gt;
 &lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
 &lt;script&gt;
-var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"font":{"size":12},"line":{"color":"black"},"values":[["ARCH 22860","ARCS 12721","ID 19670","ID 19883","CMGT 19400","ARCH 13310","ARCH 14775","ARCS 11014","CMGT 17964","AED 22860","CMGT 16841","ARCH 16841","ARCH 29604","ARCH 19059","ID 15409","ARCH 15217","CMGT 11015","ID 13889","ID 29543","CMGT 21745","ARCH 14841"],[22.0,10.0,56.0,68.0,97.0,98.0,84.0,12.0,103.0,11.0,68.0,348.0,87.0,27.0,61.0,152.0,39.0,57.0,68.0,129.0,101.0],[1.0,0.0,5.0,4.0,8.0,9.0,6.0,2.0,12.0,1.0,6.0,43.0,11.0,5.0,11.0,18.0,5.0,8.0,9.0,23.0,18.0],[1.0,1.0,2.0,5.0,5.0,6.0,7.0,0.0,6.0,1.0,7.0,26.0,7.0,1.0,3.0,17.0,4.0,6.0,8.0,10.0,9.0],[20.0,9.0,49.0,59.0,84.0,83.0,71.0,10.0,85.0,9.0,55.0,279.0,69.0,21.0,47.0,117.0,30.0,43.0,51.0,96.0,74.0],["90.91%","90.00%","87.50%","86.76%","86.60%","84.69%","84.52%","83.33%","82.52%","81.82%","80.88%","80.17%","79.31%","77.78%","77.05%","76.97%","76.92%","75.44%","75.00%","74.42%","73.27%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":true,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFCC"]]},"line":{"color":"black"},"values":[["AED 22860"],[11.0],[1.0],[1.0],[9.0],["81.82%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["ARCH 22860","ARCH 13310","ARCH 14775","ARCH 16841","ARCH 29604","ARCH 19059","ARCH 15217","ARCH 14841"],[22.0,98.0,84.0,348.0,87.0,27.0,152.0,101.0],[1.0,9.0,6.0,43.0,11.0,5.0,18.0,18.0],[1.0,6.0,7.0,26.0,7.0,1.0,17.0,9.0],[20.0,83.0,71.0,279.0,69.0,21.0,117.0,74.0],["90.91%","84.69%","84.52%","80.17%","79.31%","77.78%","76.97%","73.27%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC"]]},"line":{"color":"black"},"values":[["ARCS 12721","ARCS 11014"],[10.0,12.0],[0.0,2.0],[1.0,0.0],[9.0,10.0],["90.00%","83.33%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["CMGT 19400","CMGT 17964","CMGT 16841","CMGT 11015","CMGT 21745"],[97.0,103.0,68.0,39.0,129.0],[8.0,12.0,6.0,5.0,23.0],[5.0,6.0,7.0,4.0,10.0],[84.0,85.0,55.0,30.0,96.0],["86.60%","82.52%","80.88%","76.92%","74.42%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["ID 19670","ID 19883","ID 15409","ID 13889","ID 29543"],[56.0,68.0,61.0,57.0,68.0],[5.0,4.0,11.0,8.0,9.0],[2.0,5.0,3.0,6.0,8.0],[49.0,59.0,47.0,43.0,51.0],["87.50%","86.76%","77.05%","75.44%","75.00%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"lightslategray"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"}],"layout":{"height":650,"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CAED Midterm Report","x":0.5,"xanchor":"center","y":0.965,"yanchor":"top"},"width":1200,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"font":{"family":"Segoe UI"},"updatemenus":[{"buttons":[{"args":[{"visible":[true,false,false,false,false,false]}],"label":"All","method":"update"},{"args":[{"visible":[false,true,false,false,false,false]}],"label":"AED","method":"update"},{"args":[{"visible":[false,false,true,false,false,false]}],"label":"ARCH","method":"update"},{"args":[{"visible":[false,false,false,true,false,false]}],"label":"ARCS","method":"update"},{"args":[{"visible":[false,false,false,false,true,false]}],"label":"CMGT","method":"update"},{"args":[{"visible":[false,false,false,false,false,true]}],"label":"ID","method":"update"}],"direction":"down","showactive":true,"type":"dropdown","x":0.5,"xanchor":"center","y":1.1,"yanchor":"top"}],"annotations":[{"showarrow":false,"text":"\u003cb\u003eSubject:\u003c\u002fb\u003e","x":0.435,"xanchor":"center","y":1.0875,"yanchor":"top","font":{"size":14,"color":"black"}}]}};
+var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"font":{"size":12},"line":{"color":"black"},"values":[["ARCH 22860","ARCS 12721","ID 19670","ID 19883","CMGT 19400","ARCH 13310","ARCH 14775","ARCS 11014","CMGT 17964","AED 22860","CMGT 16841","ARCH 16841","ARCH 29604","ARCH 19059","ID 15409","ARCH 15217","CMGT 11015","ID 13889","ID 29543","CMGT 21745","ARCH 14841"],[22.0,10.0,56.0,68.0,97.0,98.0,84.0,12.0,103.0,11.0,68.0,348.0,87.0,27.0,61.0,152.0,39.0,57.0,68.0,129.0,101.0],[1.0,0.0,5.0,4.0,8.0,9.0,6.0,2.0,12.0,1.0,6.0,43.0,11.0,5.0,11.0,18.0,5.0,8.0,9.0,23.0,18.0],[1.0,1.0,2.0,5.0,5.0,6.0,7.0,0.0,6.0,1.0,7.0,26.0,7.0,1.0,3.0,17.0,4.0,6.0,8.0,10.0,9.0],[20.0,9.0,49.0,59.0,84.0,83.0,71.0,10.0,85.0,9.0,55.0,279.0,69.0,21.0,47.0,117.0,30.0,43.0,51.0,96.0,74.0],["90.91%","90.00%","87.50%","86.76%","86.60%","84.69%","84.52%","83.33%","82.52%","81.82%","80.88%","80.17%","79.31%","77.78%","77.05%","76.97%","76.92%","75.44%","75.00%","74.42%","73.27%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":true,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFCC"]]},"line":{"color":"black"},"values":[["AED 22860"],[11.0],[1.0],[1.0],[9.0],["81.82%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["ARCH 22860","ARCH 13310","ARCH 14775","ARCH 16841","ARCH 29604","ARCH 19059","ARCH 15217","ARCH 14841"],[22.0,98.0,84.0,348.0,87.0,27.0,152.0,101.0],[1.0,9.0,6.0,43.0,11.0,5.0,18.0,18.0],[1.0,6.0,7.0,26.0,7.0,1.0,17.0,9.0],[20.0,83.0,71.0,279.0,69.0,21.0,117.0,74.0],["90.91%","84.69%","84.52%","80.17%","79.31%","77.78%","76.97%","73.27%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC"]]},"line":{"color":"black"},"values":[["ARCS 12721","ARCS 11014"],[10.0,12.0],[0.0,2.0],[1.0,0.0],[9.0,10.0],["90.00%","83.33%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#FFFFCC","#FFFFCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["CMGT 19400","CMGT 17964","CMGT 16841","CMGT 11015","CMGT 21745"],[97.0,103.0,68.0,39.0,129.0],[8.0,12.0,6.0,5.0,23.0],[5.0,6.0,7.0,4.0,10.0],[84.0,85.0,55.0,30.0,96.0],["86.60%","82.52%","80.88%","76.92%","74.42%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"},{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF","#FFF1CC","#FFFFFF"],["#CCFFCC","#CCFFCC","#FFCCCC","#FFCCCC","#FFCCCC"]]},"line":{"color":"black"},"values":[["ID 19670","ID 19883","ID 15409","ID 13889","ID 29543"],[56.0,68.0,61.0,57.0,68.0],[5.0,4.0,11.0,8.0,9.0],[2.0,5.0,3.0,6.0,8.0],[49.0,59.0,47.0,43.0,51.0],["87.50%","86.76%","77.05%","75.44%","75.00%"]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","size":12,"weight":"bold"},"line":{"color":"black"},"values":["Course Code","Total","MT C-, D, F, W","MT Not Reported","MT C or Higher","% of Passing Grades"]},"visible":false,"type":"table"}],"layout":{"height":650,"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CAED Midterm Report","x":0.5,"xanchor":"center","y":0.965,"yanchor":"top"},"width":1200,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"font":{"family":"Segoe UI"},"updatemenus":[{"buttons":[{"args":[{"visible":[true,false,false,false,false,false]}],"label":"All","method":"update"},{"args":[{"visible":[false,true,false,false,false,false]}],"label":"AED","method":"update"},{"args":[{"visible":[false,false,true,false,false,false]}],"label":"ARCH","method":"update"},{"args":[{"visible":[false,false,false,true,false,false]}],"label":"ARCS","method":"update"},{"args":[{"visible":[false,false,false,false,true,false]}],"label":"CMGT","method":"update"},{"args":[{"visible":[false,false,false,false,false,true]}],"label":"ID","method":"update"}],"direction":"down","showactive":true,"type":"dropdown","x":0.5,"xanchor":"center","y":1.1,"yanchor":"top"}],"annotations":[{"showarrow":false,"text":"\u003cb\u003eSubject:\u003c\u002fb\u003e","x":0.435,"xanchor":"center","y":1.0875,"yanchor":"top","font":{"size":14,"color":"black"}}]}};
 function renderPlot() {
     var container = document.getElementById('plotly-div');
     if (container) {
@@ -989,7 +989,7 @@
 &lt;div id="plotly-div"&gt;&lt;/div&gt;
 &lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
 &lt;script&gt;
-var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#E3E6E8","#EFAB00"],["#FFFFFF","#E3E6E8","#EFAB00"],["#FFFFFF","#E3E6E8","#EFAB00"]]},"font":{"color":"black"},"line":{"color":"black"},"values":[[1,2," "],["CAED Major, FR or SO, CAED Course, midterm D+ or below, still registered","CAED Major, JR or SR, CAED Course, midterm F, still registered","Total"],[[84],[14],[98]]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","weight":"bold"},"line":{"color":"black"},"values":["Group #","CAED Midterm Intervention - Student Criteria","# of Instances"]},"visible":true,"type":"table"}],"layout":{"font":{"family":"Segoe UI"},"height":280,"margin":{"b":20,"l":20,"r":20,"t":80},"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CAED Advisor Intervention Table","x":0.5,"xanchor":"center"},"width":700,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}}}};
+var fig = {"data":[{"cells":{"fill":{"color":[["#FFFFFF","#FFF1CC","#EFAB00"],["#FFFFFF","#FFF1CC","#EFAB00"],["#FFFFFF","#FFF1CC","#EFAB00"]]},"font":{"color":"black"},"line":{"color":"black"},"values":[[1,2," "],["CAED Major, FR or SO, CAED Course, midterm D+ or below, still registered","CAED Major, JR or SR, CAED Course, midterm F, still registered","Total"],[[84],[14],[98]]]},"header":{"fill":{"color":"#EFAB00"},"font":{"color":"black","weight":"bold"},"line":{"color":"black"},"values":["Group #","CAED Midterm Intervention - Student Criteria","# of Instances"]},"visible":true,"type":"table"}],"layout":{"font":{"family":"Segoe UI"},"height":280,"margin":{"b":20,"l":20,"r":20,"t":80},"title":{"font":{"color":"black","size":24,"weight":"bold"},"text":"\u003cb\u003eSpring 2026 CAED Advisor Intervention Table","x":0.5,"xanchor":"center"},"width":700,"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}}}};
 function renderPlot() {
     var container = document.getElementById('plotly-div');
     if (container) {
@@ -1109,7 +1109,7 @@
 &lt;div id="plotly-div"&gt;&lt;/div&gt;
 &lt;script src="https://cdn.plot.ly/plotly-latest.min.js"&gt;&lt;/script&gt;
 &lt;script&gt;
-var fig = {"data":[{"customdata":["Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of D+ or lower"],"hovertemplate":"\u003cb\u003eFR\u002fSO Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions Needed: %{y}\u003cbr\u003e%{customdata}\u003cextra\u003e\u003c\u002fextra\u003e","line":{"color":"#003976","width":2},"name":"FR\u002fSO Interventions Needed","x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[424,392,442,404,406,363,417,268],"type":"scatter"},{"hovertemplate":"\u003cb\u003eJR\u002fSR Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions Needed: %{y}\u003cbr\u003eCriteria: MT Grade of F\u003cextra\u003e\u003c\u002fextra\u003e","line":{"color":"#EFAB00","width":2},"name":"JR\u002fSR Interventions Needed","x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[37,35,30,38,51,46,24,40],"type":"scatter"},{"hovertemplate":"\u003cb\u003eTotal Number of Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions: %{text}\u003cextra\u003e\u003c\u002fextra\u003e","mode":"text","name":"Total Interventions (n)","showlegend":true,"text":["461","427","472","442","457","409","441","308"],"textfont":{"weight":"bold"},"x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[-12,-12,-12,-12,-12,-12,-12,-12],"type":"scatter"}],"layout":{"font":{"family":"Segoe UI"},"legend":{"orientation":"h","title":{"font":{"color":"black"},"text":"\u003cb\u003eLegend:\u003c\u002fb\u003e"},"x":0.5,"xanchor":"center","y":-0.4,"yanchor":"bottom"},"title":{"font":{"color":"black","size":24},"text":"\u003cb\u003eCotA Interventions Needed Over Time\u003c\u002fb\u003e","x":0.5,"xanchor":"center","y":0.93,"yanchor":"top"},"xaxis":{"title":{"font":{"size":18},"text":"\u003ci\u003eSemester\u003c\u002fi\u003e"}},"yaxis":{"dtick":75,"range":[-20,475],"title":{"font":{"size":18},"text":"\u003ci\u003e# of Intervention\u003c\u002fi\u003e"}},"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"margin":{"l":20,"r":20,"b":20,"t":80},"shapes":[{"fillcolor":"white","layer":"below","line":{"color":"black","width":1},"type":"rect","x0":0,"x1":1,"xref":"paper","y0":-19,"y1":10,"yref":"y"}],"height":350,"width":1200,"annotations":[{"ax":0,"ay":-40,"font":{"size":10},"text":"Change in\u003cbr\u003eFR\u002fSO Criteria","x":7,"y":268}]}};
+var fig = {"data":[{"customdata":["Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of C or below","Criteria: MT Grade of D+ or lower"],"hovertemplate":"\u003cb\u003eFR\u002fSO Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions Needed: %{y}\u003cbr\u003e%{customdata}\u003cextra\u003e\u003c\u002fextra\u003e","line":{"color":"#003976","width":2},"name":"FR\u002fSO Interventions Needed","x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[424,392,442,404,406,363,417,268],"type":"scatter"},{"hovertemplate":"\u003cb\u003eJR\u002fSR Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions Needed: %{y}\u003cbr\u003eCriteria: MT Grade of F\u003cextra\u003e\u003c\u002fextra\u003e","line":{"color":"#EFAB00","width":2},"name":"JR\u002fSR Interventions Needed","x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[37,35,30,38,51,46,24,40],"type":"scatter"},{"hovertemplate":"\u003cb\u003eTotal Number of Interventions\u003c\u002fb\u003e\u003cbr\u003eTerm: %{x}\u003cbr\u003e# of Interventions: %{text}\u003cextra\u003e\u003c\u002fextra\u003e","mode":"text","name":"Total Interventions (n)","showlegend":true,"text":["461","427","472","442","457","409","441","308"],"textfont":{"weight":"bold"},"x":["Fall 2022","Spring 2023","Fall 2023","Spring 2024","Fall 2024","Spring 2025","Fall 2025","Spring 2026"],"y":[-5,-5,-5,-5,-5,-5,-5,-5],"type":"scatter"}],"layout":{"font":{"family":"Segoe UI"},"legend":{"orientation":"h","title":{"font":{"color":"black"},"text":"\u003cb\u003eLegend:\u003c\u002fb\u003e"},"x":0.5,"xanchor":"center","y":-0.4,"yanchor":"bottom"},"title":{"font":{"color":"black","size":24},"text":"\u003cb\u003eCotA Interventions Needed Over Time\u003c\u002fb\u003e","x":0.5,"xanchor":"center","y":0.93,"yanchor":"top"},"xaxis":{"title":{"font":{"size":18},"text":"\u003ci\u003eSemester\u003c\u002fi\u003e"}},"yaxis":{"dtick":75,"range":[-20,475],"title":{"font":{"size":18},"text":"\u003ci\u003e# of Intervention\u003c\u002fi\u003e"}},"template":{"data":{"histogram2dcontour":[{"type":"histogram2dcontour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"choropleth":[{"type":"choropleth","colorbar":{"outlinewidth":0,"ticks":""}}],"histogram2d":[{"type":"histogram2d","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"heatmap":[{"type":"heatmap","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"contourcarpet":[{"type":"contourcarpet","colorbar":{"outlinewidth":0,"ticks":""}}],"contour":[{"type":"contour","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"surface":[{"type":"surface","colorbar":{"outlinewidth":0,"ticks":""},"colorscale":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]]}],"mesh3d":[{"type":"mesh3d","colorbar":{"outlinewidth":0,"ticks":""}}],"scatter":[{"fillpattern":{"fillmode":"overlay","size":10,"solidity":0.2},"type":"scatter"}],"parcoords":[{"type":"parcoords","line":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolargl":[{"type":"scatterpolargl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"bar":[{"error_x":{"color":"#2a3f5f"},"error_y":{"color":"#2a3f5f"},"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"bar"}],"scattergeo":[{"type":"scattergeo","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterpolar":[{"type":"scatterpolar","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"histogram":[{"marker":{"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"histogram"}],"scattergl":[{"type":"scattergl","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatter3d":[{"type":"scatter3d","line":{"colorbar":{"outlinewidth":0,"ticks":""}},"marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermap":[{"type":"scattermap","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattermapbox":[{"type":"scattermapbox","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scatterternary":[{"type":"scatterternary","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"scattercarpet":[{"type":"scattercarpet","marker":{"colorbar":{"outlinewidth":0,"ticks":""}}}],"carpet":[{"aaxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"baxis":{"endlinecolor":"#2a3f5f","gridcolor":"white","linecolor":"white","minorgridcolor":"white","startlinecolor":"#2a3f5f"},"type":"carpet"}],"table":[{"cells":{"fill":{"color":"#EBF0F8"},"line":{"color":"white"}},"header":{"fill":{"color":"#C8D4E3"},"line":{"color":"white"}},"type":"table"}],"barpolar":[{"marker":{"line":{"color":"#E5ECF6","width":0.5},"pattern":{"fillmode":"overlay","size":10,"solidity":0.2}},"type":"barpolar"}],"pie":[{"automargin":true,"type":"pie"}]},"layout":{"autotypenumbers":"strict","colorway":["#636efa","#EF553B","#00cc96","#ab63fa","#FFA15A","#19d3f3","#FF6692","#B6E880","#FF97FF","#FECB52"],"font":{"color":"#2a3f5f"},"hovermode":"closest","hoverlabel":{"align":"left"},"paper_bgcolor":"white","plot_bgcolor":"#E5ECF6","polar":{"bgcolor":"#E5ECF6","angularaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"radialaxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"ternary":{"bgcolor":"#E5ECF6","aaxis":{"gridcolor":"white","linecolor":"white","ticks":""},"baxis":{"gridcolor":"white","linecolor":"white","ticks":""},"caxis":{"gridcolor":"white","linecolor":"white","ticks":""}},"coloraxis":{"colorbar":{"outlinewidth":0,"ticks":""}},"colorscale":{"sequential":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"sequentialminus":[[0.0,"#0d0887"],[0.1111111111111111,"#46039f"],[0.2222222222222222,"#7201a8"],[0.3333333333333333,"#9c179e"],[0.4444444444444444,"#bd3786"],[0.5555555555555556,"#d8576b"],[0.6666666666666666,"#ed7953"],[0.7777777777777778,"#fb9f3a"],[0.8888888888888888,"#fdca26"],[1.0,"#f0f921"]],"diverging":[[0,"#8e0152"],[0.1,"#c51b7d"],[0.2,"#de77ae"],[0.3,"#f1b6da"],[0.4,"#fde0ef"],[0.5,"#f7f7f7"],[0.6,"#e6f5d0"],[0.7,"#b8e186"],[0.8,"#7fbc41"],[0.9,"#4d9221"],[1,"#276419"]]},"xaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"yaxis":{"gridcolor":"white","linecolor":"white","ticks":"","title":{"standoff":15},"zerolinecolor":"white","automargin":true,"zerolinewidth":2},"scene":{"xaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"yaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2},"zaxis":{"backgroundcolor":"#E5ECF6","gridcolor":"white","linecolor":"white","showbackground":true,"ticks":"","zerolinecolor":"white","gridwidth":2}},"shapedefaults":{"line":{"color":"#2a3f5f"}},"annotationdefaults":{"arrowcolor":"#2a3f5f","arrowhead":0,"arrowwidth":1},"geo":{"bgcolor":"white","landcolor":"#E5ECF6","subunitcolor":"white","showland":true,"showlakes":true,"lakecolor":"white"},"title":{"x":0.05},"mapbox":{"style":"light"}}},"margin":{"l":20,"r":20,"b":20,"t":80},"shapes":[{"fillcolor":"white","layer":"below","line":{"color":"black","width":1},"type":"rect","x0":0,"x1":1,"xref":"paper","y0":-19,"y1":15,"yref":"y"}],"height":350,"width":1200,"annotations":[{"ax":0,"ay":-40,"font":{"size":10},"text":"Change in\u003cbr\u003eFR\u002fSO Criteria","x":7,"y":268}]}};
 function renderPlot() {
     var container = document.getElementById('plotly-div');
     if (container) {
